--- a/РАБОЧИЙ СТОЛ/расчеты Останкино СЫРЫ/дв 20,10,26 млрсч ост сыр.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты Останкино СЫРЫ/дв 20,10,26 млрсч ост сыр.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино СЫРЫ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино СЫРЫ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{546578A5-8455-4247-9C0F-96652ABDD086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AA9A225-E842-467C-AD0D-3F89F851556D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,15 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AG$48</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1182,81 +1190,81 @@
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="4">
-        <f>SUM(K6:K499)</f>
+        <f t="shared" ref="K5:R5" si="0">SUM(K6:K499)</f>
         <v>5545</v>
       </c>
       <c r="L5" s="4">
-        <f>SUM(L6:L499)</f>
+        <f t="shared" si="0"/>
         <v>-1192.7139999999999</v>
       </c>
       <c r="M5" s="4">
-        <f>SUM(M6:M499)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <f>SUM(N6:N499)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O5" s="4">
-        <f>SUM(O6:O499)</f>
+        <f t="shared" si="0"/>
         <v>12146</v>
       </c>
       <c r="P5" s="4">
-        <f>SUM(P6:P499)</f>
+        <f t="shared" si="0"/>
         <v>870.45720000000017</v>
       </c>
       <c r="Q5" s="4">
-        <f>SUM(Q6:Q499)</f>
+        <f t="shared" si="0"/>
         <v>3105.8</v>
       </c>
       <c r="R5" s="4">
-        <f>SUM(R6:R499)</f>
+        <f t="shared" si="0"/>
         <v>1600</v>
       </c>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
       <c r="U5" s="4">
-        <f>SUM(U6:U499)</f>
+        <f t="shared" ref="U5:AE5" si="1">SUM(U6:U499)</f>
         <v>751.99880000000019</v>
       </c>
       <c r="V5" s="4">
-        <f>SUM(V6:V499)</f>
+        <f t="shared" si="1"/>
         <v>537.97480000000007</v>
       </c>
       <c r="W5" s="4">
-        <f>SUM(W6:W499)</f>
+        <f t="shared" si="1"/>
         <v>412.95440000000002</v>
       </c>
       <c r="X5" s="4">
-        <f>SUM(X6:X499)</f>
+        <f t="shared" si="1"/>
         <v>445.22800000000001</v>
       </c>
       <c r="Y5" s="4">
-        <f>SUM(Y6:Y499)</f>
+        <f t="shared" si="1"/>
         <v>580.45000000000027</v>
       </c>
       <c r="Z5" s="4">
-        <f>SUM(Z6:Z499)</f>
+        <f t="shared" si="1"/>
         <v>287.91800000000001</v>
       </c>
       <c r="AA5" s="4">
-        <f>SUM(AA6:AA499)</f>
+        <f t="shared" si="1"/>
         <v>671.04299999999989</v>
       </c>
       <c r="AB5" s="4">
-        <f>SUM(AB6:AB499)</f>
+        <f t="shared" si="1"/>
         <v>442.24200000000002</v>
       </c>
       <c r="AC5" s="4">
-        <f>SUM(AC6:AC499)</f>
+        <f t="shared" si="1"/>
         <v>538.77160000000015</v>
       </c>
       <c r="AD5" s="4">
-        <f>SUM(AD6:AD499)</f>
+        <f t="shared" si="1"/>
         <v>469.94360000000006</v>
       </c>
       <c r="AE5" s="4">
-        <f>SUM(AE6:AE499)</f>
+        <f t="shared" si="1"/>
         <v>801.44040000000018</v>
       </c>
       <c r="AF5" s="1"/>
@@ -1312,7 +1320,7 @@
         <v>64</v>
       </c>
       <c r="L6" s="1">
-        <f t="shared" ref="L6:L48" si="0">E6-K6</f>
+        <f t="shared" ref="L6:L48" si="2">E6-K6</f>
         <v>-1.3900000000000006</v>
       </c>
       <c r="M6" s="1"/>
@@ -1369,7 +1377,7 @@
       </c>
       <c r="AF6" s="1"/>
       <c r="AG6" s="1">
-        <f>G6*Q6</f>
+        <f t="shared" ref="AG6:AG24" si="3">G6*Q6</f>
         <v>0</v>
       </c>
       <c r="AH6" s="1"/>
@@ -1418,7 +1426,7 @@
         <v>10</v>
       </c>
       <c r="L7" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-0.77200000000000024</v>
       </c>
       <c r="M7" s="1"/>
@@ -1427,17 +1435,17 @@
         <v>198</v>
       </c>
       <c r="P7" s="1">
-        <f t="shared" ref="P7:P48" si="1">E7/5</f>
+        <f t="shared" ref="P7:P48" si="4">E7/5</f>
         <v>1.8455999999999999</v>
       </c>
       <c r="Q7" s="5"/>
       <c r="R7" s="5"/>
       <c r="S7" s="1">
-        <f t="shared" ref="S7:S48" si="2">(F7+O7+Q7)/P7</f>
+        <f t="shared" ref="S7:S48" si="5">(F7+O7+Q7)/P7</f>
         <v>119.82444733420026</v>
       </c>
       <c r="T7" s="1">
-        <f t="shared" ref="T7:T48" si="3">(F7+O7)/P7</f>
+        <f t="shared" ref="T7:T48" si="6">(F7+O7)/P7</f>
         <v>119.82444733420026</v>
       </c>
       <c r="U7" s="1">
@@ -1477,7 +1485,7 @@
         <v>40</v>
       </c>
       <c r="AG7" s="1">
-        <f>G7*Q7</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH7" s="1"/>
@@ -1524,14 +1532,14 @@
         <v>34</v>
       </c>
       <c r="L8" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-10</v>
       </c>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>4.8</v>
       </c>
       <c r="Q8" s="5">
@@ -1540,11 +1548,11 @@
       </c>
       <c r="R8" s="5"/>
       <c r="S8" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="T8" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U8" s="1">
@@ -1584,7 +1592,7 @@
         <v>91</v>
       </c>
       <c r="AG8" s="1">
-        <f>G8*Q8</f>
+        <f t="shared" si="3"/>
         <v>47.491199999999999</v>
       </c>
       <c r="AH8" s="1"/>
@@ -1633,7 +1641,7 @@
         <v>228</v>
       </c>
       <c r="L9" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-220</v>
       </c>
       <c r="M9" s="1"/>
@@ -1642,17 +1650,17 @@
         <v>396</v>
       </c>
       <c r="P9" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>1.6</v>
       </c>
       <c r="Q9" s="5"/>
       <c r="R9" s="5"/>
       <c r="S9" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>246.875</v>
       </c>
       <c r="T9" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>246.875</v>
       </c>
       <c r="U9" s="1">
@@ -1690,7 +1698,7 @@
       </c>
       <c r="AF9" s="1"/>
       <c r="AG9" s="1">
-        <f>G9*Q9</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH9" s="1"/>
@@ -1739,7 +1747,7 @@
         <v>393</v>
       </c>
       <c r="L10" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-226</v>
       </c>
       <c r="M10" s="1"/>
@@ -1748,20 +1756,20 @@
         <v>396</v>
       </c>
       <c r="P10" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>33.4</v>
       </c>
       <c r="Q10" s="5">
-        <f t="shared" ref="Q10:Q19" si="4">17*P10-O10-F10</f>
+        <f t="shared" ref="Q10:Q19" si="7">17*P10-O10-F10</f>
         <v>174.79999999999995</v>
       </c>
       <c r="R10" s="5"/>
       <c r="S10" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>17</v>
       </c>
       <c r="T10" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>11.766467065868264</v>
       </c>
       <c r="U10" s="1">
@@ -1801,7 +1809,7 @@
         <v>43</v>
       </c>
       <c r="AG10" s="1">
-        <f>G10*Q10</f>
+        <f t="shared" si="3"/>
         <v>130.05119999999997</v>
       </c>
       <c r="AH10" s="1"/>
@@ -1852,7 +1860,7 @@
         <v>363</v>
       </c>
       <c r="L11" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-278</v>
       </c>
       <c r="M11" s="1"/>
@@ -1861,17 +1869,17 @@
         <v>600</v>
       </c>
       <c r="P11" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>17</v>
       </c>
       <c r="Q11" s="5"/>
       <c r="R11" s="5"/>
       <c r="S11" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>36</v>
       </c>
       <c r="T11" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>36</v>
       </c>
       <c r="U11" s="1">
@@ -1909,7 +1917,7 @@
       </c>
       <c r="AF11" s="1"/>
       <c r="AG11" s="1">
-        <f>G11*Q11</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH11" s="1"/>
@@ -1960,7 +1968,7 @@
         <v>435</v>
       </c>
       <c r="L12" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-255</v>
       </c>
       <c r="M12" s="1"/>
@@ -1969,17 +1977,17 @@
         <v>600</v>
       </c>
       <c r="P12" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>36</v>
       </c>
       <c r="Q12" s="5"/>
       <c r="R12" s="5"/>
       <c r="S12" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>17.083333333333332</v>
       </c>
       <c r="T12" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>17.083333333333332</v>
       </c>
       <c r="U12" s="1">
@@ -2017,7 +2025,7 @@
       </c>
       <c r="AF12" s="1"/>
       <c r="AG12" s="1">
-        <f>G12*Q12</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH12" s="1"/>
@@ -2068,7 +2076,7 @@
         <v>33</v>
       </c>
       <c r="L13" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-2</v>
       </c>
       <c r="M13" s="1"/>
@@ -2077,17 +2085,17 @@
         <v>48</v>
       </c>
       <c r="P13" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>6.2</v>
       </c>
       <c r="Q13" s="5"/>
       <c r="R13" s="5"/>
       <c r="S13" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>19.677419354838708</v>
       </c>
       <c r="T13" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>19.677419354838708</v>
       </c>
       <c r="U13" s="1">
@@ -2127,7 +2135,7 @@
         <v>90</v>
       </c>
       <c r="AG13" s="1">
-        <f>G13*Q13</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH13" s="1"/>
@@ -2178,7 +2186,7 @@
         <v>87</v>
       </c>
       <c r="L14" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-1</v>
       </c>
       <c r="M14" s="1"/>
@@ -2187,20 +2195,20 @@
         <v>48</v>
       </c>
       <c r="P14" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>17.2</v>
       </c>
       <c r="Q14" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>50.399999999999977</v>
       </c>
       <c r="R14" s="5"/>
       <c r="S14" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>17</v>
       </c>
       <c r="T14" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>14.069767441860465</v>
       </c>
       <c r="U14" s="1">
@@ -2238,7 +2246,7 @@
       </c>
       <c r="AF14" s="1"/>
       <c r="AG14" s="1">
-        <f>G14*Q14</f>
+        <f t="shared" si="3"/>
         <v>9.0719999999999956</v>
       </c>
       <c r="AH14" s="1"/>
@@ -2289,7 +2297,7 @@
         <v>60</v>
       </c>
       <c r="L15" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-1</v>
       </c>
       <c r="M15" s="1"/>
@@ -2298,17 +2306,17 @@
         <v>48</v>
       </c>
       <c r="P15" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>11.8</v>
       </c>
       <c r="Q15" s="5"/>
       <c r="R15" s="5"/>
       <c r="S15" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>22.288135593220339</v>
       </c>
       <c r="T15" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>22.288135593220339</v>
       </c>
       <c r="U15" s="1">
@@ -2346,7 +2354,7 @@
       </c>
       <c r="AF15" s="1"/>
       <c r="AG15" s="1">
-        <f>G15*Q15</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH15" s="1"/>
@@ -2391,7 +2399,7 @@
         <v>23</v>
       </c>
       <c r="L16" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-2</v>
       </c>
       <c r="M16" s="1"/>
@@ -2400,7 +2408,7 @@
         <v>48</v>
       </c>
       <c r="P16" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>4.2</v>
       </c>
       <c r="Q16" s="5">
@@ -2409,11 +2417,11 @@
       </c>
       <c r="R16" s="5"/>
       <c r="S16" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>15</v>
       </c>
       <c r="T16" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>11.428571428571429</v>
       </c>
       <c r="U16" s="1">
@@ -2453,7 +2461,7 @@
         <v>92</v>
       </c>
       <c r="AG16" s="1">
-        <f>G16*Q16</f>
+        <f t="shared" si="3"/>
         <v>1.5</v>
       </c>
       <c r="AH16" s="1"/>
@@ -2504,7 +2512,7 @@
         <v>21</v>
       </c>
       <c r="L17" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M17" s="1"/>
@@ -2513,20 +2521,20 @@
         <v>48</v>
       </c>
       <c r="P17" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>4.2</v>
       </c>
       <c r="Q17" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>21.400000000000006</v>
       </c>
       <c r="R17" s="5"/>
       <c r="S17" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>17</v>
       </c>
       <c r="T17" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>11.904761904761905</v>
       </c>
       <c r="U17" s="1">
@@ -2564,7 +2572,7 @@
       </c>
       <c r="AF17" s="1"/>
       <c r="AG17" s="1">
-        <f>G17*Q17</f>
+        <f t="shared" si="3"/>
         <v>2.1400000000000006</v>
       </c>
       <c r="AH17" s="1"/>
@@ -2615,7 +2623,7 @@
         <v>877</v>
       </c>
       <c r="L18" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
       <c r="M18" s="1"/>
@@ -2624,7 +2632,7 @@
         <v>3000</v>
       </c>
       <c r="P18" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>178.6</v>
       </c>
       <c r="Q18" s="5"/>
@@ -2636,7 +2644,7 @@
         <v>21.87010078387458</v>
       </c>
       <c r="T18" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>18.51063829787234</v>
       </c>
       <c r="U18" s="1">
@@ -2674,7 +2682,7 @@
       </c>
       <c r="AF18" s="1"/>
       <c r="AG18" s="1">
-        <f>G18*Q18</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH18" s="1"/>
@@ -2725,7 +2733,7 @@
         <v>1024</v>
       </c>
       <c r="L19" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>18</v>
       </c>
       <c r="M19" s="1"/>
@@ -2734,11 +2742,11 @@
         <v>1200</v>
       </c>
       <c r="P19" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>208.4</v>
       </c>
       <c r="Q19" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>997.80000000000018</v>
       </c>
       <c r="R19" s="5">
@@ -2749,7 +2757,7 @@
         <v>21.798464491362765</v>
       </c>
       <c r="T19" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>12.212092130518235</v>
       </c>
       <c r="U19" s="1">
@@ -2787,7 +2795,7 @@
       </c>
       <c r="AF19" s="1"/>
       <c r="AG19" s="1">
-        <f>G19*Q19</f>
+        <f t="shared" si="3"/>
         <v>179.60400000000001</v>
       </c>
       <c r="AH19" s="1"/>
@@ -2838,24 +2846,24 @@
         <v>11</v>
       </c>
       <c r="L20" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
       <c r="P20" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="Q20" s="5"/>
       <c r="R20" s="5"/>
       <c r="S20" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>17.27272727272727</v>
       </c>
       <c r="T20" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>17.27272727272727</v>
       </c>
       <c r="U20" s="1">
@@ -2893,7 +2901,7 @@
       </c>
       <c r="AF20" s="1"/>
       <c r="AG20" s="1">
-        <f>G20*Q20</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH20" s="1"/>
@@ -2944,24 +2952,24 @@
         <v>12</v>
       </c>
       <c r="L21" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
       <c r="P21" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>2.4</v>
       </c>
       <c r="Q21" s="5"/>
       <c r="R21" s="5"/>
       <c r="S21" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>22.083333333333336</v>
       </c>
       <c r="T21" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>22.083333333333336</v>
       </c>
       <c r="U21" s="1">
@@ -3001,7 +3009,7 @@
         <v>85</v>
       </c>
       <c r="AG21" s="1">
-        <f>G21*Q21</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH21" s="1"/>
@@ -3052,7 +3060,7 @@
         <v>49</v>
       </c>
       <c r="L22" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-16</v>
       </c>
       <c r="M22" s="1"/>
@@ -3061,7 +3069,7 @@
         <v>16</v>
       </c>
       <c r="P22" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>6.6</v>
       </c>
       <c r="Q22" s="5">
@@ -3070,11 +3078,11 @@
       </c>
       <c r="R22" s="5"/>
       <c r="S22" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>14</v>
       </c>
       <c r="T22" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>2.8787878787878789</v>
       </c>
       <c r="U22" s="1">
@@ -3112,7 +3120,7 @@
       </c>
       <c r="AF22" s="1"/>
       <c r="AG22" s="1">
-        <f>G22*Q22</f>
+        <f t="shared" si="3"/>
         <v>13.211999999999998</v>
       </c>
       <c r="AH22" s="1"/>
@@ -3159,7 +3167,7 @@
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M23" s="1"/>
@@ -3168,17 +3176,17 @@
         <v>252</v>
       </c>
       <c r="P23" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q23" s="5"/>
       <c r="R23" s="5"/>
       <c r="S23" s="1" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T23" s="1" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U23" s="1">
@@ -3218,7 +3226,7 @@
         <v>86</v>
       </c>
       <c r="AG23" s="1">
-        <f>G23*Q23</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH23" s="1"/>
@@ -3263,7 +3271,7 @@
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M24" s="1"/>
@@ -3272,17 +3280,17 @@
         <v>200</v>
       </c>
       <c r="P24" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q24" s="5"/>
       <c r="R24" s="5"/>
       <c r="S24" s="1" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T24" s="1" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U24" s="1">
@@ -3322,7 +3330,7 @@
         <v>87</v>
       </c>
       <c r="AG24" s="1">
-        <f>G24*Q24</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AH24" s="1"/>
@@ -3363,24 +3371,24 @@
       <c r="J25" s="9"/>
       <c r="K25" s="9"/>
       <c r="L25" s="9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M25" s="9"/>
       <c r="N25" s="9"/>
       <c r="O25" s="9"/>
       <c r="P25" s="9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q25" s="11"/>
       <c r="R25" s="11"/>
       <c r="S25" s="9" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
       <c r="T25" s="9" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U25" s="9">
@@ -3468,7 +3476,7 @@
         <v>133</v>
       </c>
       <c r="L26" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-13</v>
       </c>
       <c r="M26" s="1"/>
@@ -3477,20 +3485,20 @@
         <v>300</v>
       </c>
       <c r="P26" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>24</v>
       </c>
       <c r="Q26" s="5">
-        <f t="shared" ref="Q26:Q43" si="5">17*P26-O26-F26</f>
+        <f t="shared" ref="Q26:Q43" si="8">17*P26-O26-F26</f>
         <v>107</v>
       </c>
       <c r="R26" s="5"/>
       <c r="S26" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>17</v>
       </c>
       <c r="T26" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>12.541666666666666</v>
       </c>
       <c r="U26" s="1">
@@ -3528,7 +3536,7 @@
       </c>
       <c r="AF26" s="1"/>
       <c r="AG26" s="1">
-        <f>G26*Q26</f>
+        <f t="shared" ref="AG26:AG48" si="9">G26*Q26</f>
         <v>19.259999999999998</v>
       </c>
       <c r="AH26" s="1"/>
@@ -3579,7 +3587,7 @@
         <v>23</v>
       </c>
       <c r="L27" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M27" s="1"/>
@@ -3588,17 +3596,17 @@
         <v>152</v>
       </c>
       <c r="P27" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>4.5999999999999996</v>
       </c>
       <c r="Q27" s="5"/>
       <c r="R27" s="5"/>
       <c r="S27" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>42.391304347826093</v>
       </c>
       <c r="T27" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>42.391304347826093</v>
       </c>
       <c r="U27" s="1">
@@ -3638,7 +3646,7 @@
         <v>40</v>
       </c>
       <c r="AG27" s="1">
-        <f>G27*Q27</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AH27" s="1"/>
@@ -3687,7 +3695,7 @@
         <v>29</v>
       </c>
       <c r="L28" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-5</v>
       </c>
       <c r="M28" s="1"/>
@@ -3696,17 +3704,17 @@
         <v>248</v>
       </c>
       <c r="P28" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>4.8</v>
       </c>
       <c r="Q28" s="5"/>
       <c r="R28" s="5"/>
       <c r="S28" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>51.666666666666671</v>
       </c>
       <c r="T28" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>51.666666666666671</v>
       </c>
       <c r="U28" s="1">
@@ -3744,7 +3752,7 @@
       </c>
       <c r="AF28" s="1"/>
       <c r="AG28" s="1">
-        <f>G28*Q28</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AH28" s="1"/>
@@ -3793,7 +3801,7 @@
         <v>30</v>
       </c>
       <c r="L29" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M29" s="1"/>
@@ -3802,17 +3810,17 @@
         <v>200</v>
       </c>
       <c r="P29" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
       <c r="Q29" s="5"/>
       <c r="R29" s="5"/>
       <c r="S29" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>42.166666666666664</v>
       </c>
       <c r="T29" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>42.166666666666664</v>
       </c>
       <c r="U29" s="1">
@@ -3852,7 +3860,7 @@
         <v>85</v>
       </c>
       <c r="AG29" s="1">
-        <f>G29*Q29</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AH29" s="1"/>
@@ -3903,7 +3911,7 @@
         <v>152</v>
       </c>
       <c r="L30" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-69</v>
       </c>
       <c r="M30" s="1"/>
@@ -3912,20 +3920,20 @@
         <v>200</v>
       </c>
       <c r="P30" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>16.600000000000001</v>
       </c>
       <c r="Q30" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>79.200000000000045</v>
       </c>
       <c r="R30" s="5"/>
       <c r="S30" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>17</v>
       </c>
       <c r="T30" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>12.228915662650602</v>
       </c>
       <c r="U30" s="1">
@@ -3965,7 +3973,7 @@
         <v>65</v>
       </c>
       <c r="AG30" s="1">
-        <f>G30*Q30</f>
+        <f t="shared" si="9"/>
         <v>14.256000000000007</v>
       </c>
       <c r="AH30" s="1"/>
@@ -4016,7 +4024,7 @@
         <v>217</v>
       </c>
       <c r="L31" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-2</v>
       </c>
       <c r="M31" s="1"/>
@@ -4025,20 +4033,20 @@
         <v>300</v>
       </c>
       <c r="P31" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>43</v>
       </c>
       <c r="Q31" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>448</v>
       </c>
       <c r="R31" s="5"/>
       <c r="S31" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>17</v>
       </c>
       <c r="T31" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>6.5813953488372094</v>
       </c>
       <c r="U31" s="1">
@@ -4076,7 +4084,7 @@
       </c>
       <c r="AF31" s="1"/>
       <c r="AG31" s="1">
-        <f>G31*Q31</f>
+        <f t="shared" si="9"/>
         <v>80.64</v>
       </c>
       <c r="AH31" s="1"/>
@@ -4127,7 +4135,7 @@
         <v>157</v>
       </c>
       <c r="L32" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-42</v>
       </c>
       <c r="M32" s="1"/>
@@ -4136,20 +4144,20 @@
         <v>350</v>
       </c>
       <c r="P32" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="Q32" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>38</v>
       </c>
       <c r="R32" s="5"/>
       <c r="S32" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>17</v>
       </c>
       <c r="T32" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>15.347826086956522</v>
       </c>
       <c r="U32" s="1">
@@ -4187,7 +4195,7 @@
       </c>
       <c r="AF32" s="1"/>
       <c r="AG32" s="1">
-        <f>G32*Q32</f>
+        <f t="shared" si="9"/>
         <v>6.84</v>
       </c>
       <c r="AH32" s="1"/>
@@ -4238,7 +4246,7 @@
         <v>187</v>
       </c>
       <c r="L33" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-69</v>
       </c>
       <c r="M33" s="1"/>
@@ -4247,20 +4255,20 @@
         <v>300</v>
       </c>
       <c r="P33" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>23.6</v>
       </c>
       <c r="Q33" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>89.200000000000045</v>
       </c>
       <c r="R33" s="5"/>
       <c r="S33" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>17</v>
       </c>
       <c r="T33" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>13.220338983050846</v>
       </c>
       <c r="U33" s="1">
@@ -4298,7 +4306,7 @@
       </c>
       <c r="AF33" s="1"/>
       <c r="AG33" s="1">
-        <f>G33*Q33</f>
+        <f t="shared" si="9"/>
         <v>16.056000000000008</v>
       </c>
       <c r="AH33" s="1"/>
@@ -4349,7 +4357,7 @@
         <v>248</v>
       </c>
       <c r="L34" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-2</v>
       </c>
       <c r="M34" s="1"/>
@@ -4358,20 +4366,20 @@
         <v>300</v>
       </c>
       <c r="P34" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>49.2</v>
       </c>
       <c r="Q34" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>493.40000000000009</v>
       </c>
       <c r="R34" s="5"/>
       <c r="S34" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>17</v>
       </c>
       <c r="T34" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>6.9715447154471537</v>
       </c>
       <c r="U34" s="1">
@@ -4409,7 +4417,7 @@
       </c>
       <c r="AF34" s="1"/>
       <c r="AG34" s="1">
-        <f>G34*Q34</f>
+        <f t="shared" si="9"/>
         <v>88.812000000000012</v>
       </c>
       <c r="AH34" s="1"/>
@@ -4460,7 +4468,7 @@
         <v>119</v>
       </c>
       <c r="L35" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-17</v>
       </c>
       <c r="M35" s="1"/>
@@ -4469,20 +4477,20 @@
         <v>300</v>
       </c>
       <c r="P35" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>20.399999999999999</v>
       </c>
       <c r="Q35" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>40.799999999999955</v>
       </c>
       <c r="R35" s="5"/>
       <c r="S35" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>17</v>
       </c>
       <c r="T35" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>15.000000000000002</v>
       </c>
       <c r="U35" s="1">
@@ -4522,7 +4530,7 @@
         <v>71</v>
       </c>
       <c r="AG35" s="1">
-        <f>G35*Q35</f>
+        <f t="shared" si="9"/>
         <v>7.3439999999999914</v>
       </c>
       <c r="AH35" s="1"/>
@@ -4573,14 +4581,14 @@
         <v>54</v>
       </c>
       <c r="L36" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-1</v>
       </c>
       <c r="M36" s="1"/>
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
       <c r="P36" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>10.6</v>
       </c>
       <c r="Q36" s="5">
@@ -4589,11 +4597,11 @@
       </c>
       <c r="R36" s="5"/>
       <c r="S36" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
       <c r="T36" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>10.660377358490566</v>
       </c>
       <c r="U36" s="1">
@@ -4631,7 +4639,7 @@
       </c>
       <c r="AF36" s="1"/>
       <c r="AG36" s="1">
-        <f>G36*Q36</f>
+        <f t="shared" si="9"/>
         <v>7.9240000000000004</v>
       </c>
       <c r="AH36" s="1"/>
@@ -4682,7 +4690,7 @@
         <v>98</v>
       </c>
       <c r="L37" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-1</v>
       </c>
       <c r="M37" s="1"/>
@@ -4691,17 +4699,17 @@
         <v>304</v>
       </c>
       <c r="P37" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>19.399999999999999</v>
       </c>
       <c r="Q37" s="5"/>
       <c r="R37" s="5"/>
       <c r="S37" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>23.608247422680414</v>
       </c>
       <c r="T37" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>23.608247422680414</v>
       </c>
       <c r="U37" s="1">
@@ -4739,7 +4747,7 @@
       </c>
       <c r="AF37" s="1"/>
       <c r="AG37" s="1">
-        <f>G37*Q37</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AH37" s="1"/>
@@ -4790,7 +4798,7 @@
         <v>9</v>
       </c>
       <c r="L38" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.30400000000000027</v>
       </c>
       <c r="M38" s="1"/>
@@ -4799,17 +4807,17 @@
         <v>297</v>
       </c>
       <c r="P38" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>1.8608</v>
       </c>
       <c r="Q38" s="5"/>
       <c r="R38" s="5"/>
       <c r="S38" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>193.79245485812552</v>
       </c>
       <c r="T38" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>193.79245485812552</v>
       </c>
       <c r="U38" s="1">
@@ -4849,7 +4857,7 @@
         <v>88</v>
       </c>
       <c r="AG38" s="1">
-        <f>G38*Q38</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AH38" s="1"/>
@@ -4900,7 +4908,7 @@
         <v>10</v>
       </c>
       <c r="L39" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.3620000000000001</v>
       </c>
       <c r="M39" s="1"/>
@@ -4909,17 +4917,17 @@
         <v>297</v>
       </c>
       <c r="P39" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>2.0724</v>
       </c>
       <c r="Q39" s="5"/>
       <c r="R39" s="5"/>
       <c r="S39" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>196.64543524416138</v>
       </c>
       <c r="T39" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>196.64543524416138</v>
       </c>
       <c r="U39" s="1">
@@ -4959,7 +4967,7 @@
         <v>40</v>
       </c>
       <c r="AG39" s="1">
-        <f>G39*Q39</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AH39" s="1"/>
@@ -5010,7 +5018,7 @@
         <v>33.5</v>
       </c>
       <c r="L40" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-5.8260000000000005</v>
       </c>
       <c r="M40" s="1"/>
@@ -5019,17 +5027,17 @@
         <v>297</v>
       </c>
       <c r="P40" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>5.5347999999999997</v>
       </c>
       <c r="Q40" s="5"/>
       <c r="R40" s="5"/>
       <c r="S40" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>67.591963575919635</v>
       </c>
       <c r="T40" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>67.591963575919635</v>
       </c>
       <c r="U40" s="1">
@@ -5067,7 +5075,7 @@
       </c>
       <c r="AF40" s="1"/>
       <c r="AG40" s="1">
-        <f>G40*Q40</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AH40" s="1"/>
@@ -5118,7 +5126,7 @@
         <v>6</v>
       </c>
       <c r="L41" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-5.600000000000005E-2</v>
       </c>
       <c r="M41" s="1"/>
@@ -5127,17 +5135,17 @@
         <v>297</v>
       </c>
       <c r="P41" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>1.1888000000000001</v>
       </c>
       <c r="Q41" s="5"/>
       <c r="R41" s="5"/>
       <c r="S41" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>324.21433378196497</v>
       </c>
       <c r="T41" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>324.21433378196497</v>
       </c>
       <c r="U41" s="1">
@@ -5175,7 +5183,7 @@
       </c>
       <c r="AF41" s="1"/>
       <c r="AG41" s="1">
-        <f>G41*Q41</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AH41" s="1"/>
@@ -5224,7 +5232,7 @@
         <v>53</v>
       </c>
       <c r="L42" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="M42" s="1"/>
@@ -5233,7 +5241,7 @@
         <v>48</v>
       </c>
       <c r="P42" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>11.6</v>
       </c>
       <c r="Q42" s="5">
@@ -5242,11 +5250,11 @@
       </c>
       <c r="R42" s="5"/>
       <c r="S42" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>14.000000000000002</v>
       </c>
       <c r="T42" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>4.7413793103448274</v>
       </c>
       <c r="U42" s="1">
@@ -5286,7 +5294,7 @@
         <v>93</v>
       </c>
       <c r="AG42" s="1">
-        <f>G42*Q42</f>
+        <f t="shared" si="9"/>
         <v>10.740000000000002</v>
       </c>
       <c r="AH42" s="1"/>
@@ -5335,7 +5343,7 @@
         <v>49</v>
       </c>
       <c r="L43" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="M43" s="1"/>
@@ -5344,20 +5352,20 @@
         <v>48</v>
       </c>
       <c r="P43" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>10.4</v>
       </c>
       <c r="Q43" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>98.800000000000011</v>
       </c>
       <c r="R43" s="5"/>
       <c r="S43" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>17</v>
       </c>
       <c r="T43" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>7.5</v>
       </c>
       <c r="U43" s="1">
@@ -5395,7 +5403,7 @@
       </c>
       <c r="AF43" s="1"/>
       <c r="AG43" s="1">
-        <f>G43*Q43</f>
+        <f t="shared" si="9"/>
         <v>9.8800000000000026</v>
       </c>
       <c r="AH43" s="1"/>
@@ -5446,14 +5454,14 @@
         <v>66</v>
       </c>
       <c r="L44" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>-1</v>
       </c>
       <c r="M44" s="1"/>
       <c r="N44" s="1"/>
       <c r="O44" s="1"/>
       <c r="P44" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>13</v>
       </c>
       <c r="Q44" s="5">
@@ -5462,11 +5470,11 @@
       </c>
       <c r="R44" s="5"/>
       <c r="S44" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
       <c r="T44" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>3.9230769230769229</v>
       </c>
       <c r="U44" s="1">
@@ -5504,7 +5512,7 @@
       </c>
       <c r="AF44" s="1"/>
       <c r="AG44" s="1">
-        <f>G44*Q44</f>
+        <f t="shared" si="9"/>
         <v>21.98</v>
       </c>
       <c r="AH44" s="1"/>
@@ -5555,7 +5563,7 @@
         <v>45</v>
       </c>
       <c r="L45" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M45" s="1"/>
@@ -5564,17 +5572,17 @@
         <v>200</v>
       </c>
       <c r="P45" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="Q45" s="5"/>
       <c r="R45" s="5"/>
       <c r="S45" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>55.222222222222221</v>
       </c>
       <c r="T45" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>55.222222222222221</v>
       </c>
       <c r="U45" s="1">
@@ -5614,7 +5622,7 @@
         <v>40</v>
       </c>
       <c r="AG45" s="1">
-        <f>G45*Q45</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AH45" s="1"/>
@@ -5665,7 +5673,7 @@
         <v>28</v>
       </c>
       <c r="L46" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>4.338000000000001</v>
       </c>
       <c r="M46" s="1"/>
@@ -5674,17 +5682,17 @@
         <v>105</v>
       </c>
       <c r="P46" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>6.4676</v>
       </c>
       <c r="Q46" s="5"/>
       <c r="R46" s="5"/>
       <c r="S46" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>30.713711423093574</v>
       </c>
       <c r="T46" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>30.713711423093574</v>
       </c>
       <c r="U46" s="1">
@@ -5724,7 +5732,7 @@
         <v>94</v>
       </c>
       <c r="AG46" s="1">
-        <f>G46*Q46</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AH46" s="1"/>
@@ -5775,7 +5783,7 @@
         <v>71</v>
       </c>
       <c r="L47" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="M47" s="1"/>
@@ -5784,17 +5792,17 @@
         <v>200</v>
       </c>
       <c r="P47" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>14.4</v>
       </c>
       <c r="Q47" s="5"/>
       <c r="R47" s="5"/>
       <c r="S47" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>40.972222222222221</v>
       </c>
       <c r="T47" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>40.972222222222221</v>
       </c>
       <c r="U47" s="1">
@@ -5834,7 +5842,7 @@
         <v>95</v>
       </c>
       <c r="AG47" s="1">
-        <f>G47*Q47</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AH47" s="1"/>
@@ -5885,7 +5893,7 @@
         <v>3.5</v>
       </c>
       <c r="L48" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.32600000000000007</v>
       </c>
       <c r="M48" s="1"/>
@@ -5894,17 +5902,17 @@
         <v>105</v>
       </c>
       <c r="P48" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0.76519999999999999</v>
       </c>
       <c r="Q48" s="5"/>
       <c r="R48" s="5"/>
       <c r="S48" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>164.60010454783063</v>
       </c>
       <c r="T48" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>164.60010454783063</v>
       </c>
       <c r="U48" s="1">
@@ -5944,7 +5952,7 @@
         <v>89</v>
       </c>
       <c r="AG48" s="1">
-        <f>G48*Q48</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AH48" s="1"/>
